--- a/etf_screener/data/top-performer-b (2).xlsx
+++ b/etf_screener/data/top-performer-b (2).xlsx
@@ -1251,7 +1251,7 @@
         <v>0.46</v>
       </c>
       <c r="D2">
-        <v>3.8452054794520545</v>
+        <v>3.864383561643835</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -1263,7 +1263,7 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>11.378082191780821</v>
+        <v>11.397260273972602</v>
       </c>
       <c r="L2" t="s">
         <v>32</v>
@@ -1307,7 +1307,7 @@
         <v>0.35</v>
       </c>
       <c r="D3">
-        <v>7.363470319634703</v>
+        <v>7.382648401826483</v>
       </c>
       <c r="F3" t="s">
         <v>29</v>
@@ -1319,7 +1319,7 @@
         <v>34</v>
       </c>
       <c r="K3">
-        <v>11.758904109589041</v>
+        <v>11.778082191780822</v>
       </c>
       <c r="L3" t="s">
         <v>35</v>
@@ -1369,7 +1369,7 @@
         <v>0.75</v>
       </c>
       <c r="D4">
-        <v>8.736986301369862</v>
+        <v>8.756164383561643</v>
       </c>
       <c r="E4">
         <v>10.6</v>
@@ -1384,7 +1384,7 @@
         <v>39</v>
       </c>
       <c r="K4">
-        <v>8.736986301369862</v>
+        <v>8.756164383561643</v>
       </c>
       <c r="L4" t="s">
         <v>39</v>
@@ -1425,7 +1425,7 @@
         <v>0.35</v>
       </c>
       <c r="D5">
-        <v>6.7552511415525105</v>
+        <v>6.774429223744292</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -1437,7 +1437,7 @@
         <v>41</v>
       </c>
       <c r="K5">
-        <v>11.758904109589041</v>
+        <v>11.778082191780822</v>
       </c>
       <c r="L5" t="s">
         <v>35</v>
@@ -1490,7 +1490,7 @@
         <v>0.08</v>
       </c>
       <c r="D6">
-        <v>7.195433789954339</v>
+        <v>7.2146118721461185</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -1502,7 +1502,7 @@
         <v>43</v>
       </c>
       <c r="K6">
-        <v>11.506849315068493</v>
+        <v>11.526027397260274</v>
       </c>
       <c r="L6" t="s">
         <v>35</v>
@@ -1552,7 +1552,7 @@
         <v>0.2</v>
       </c>
       <c r="D7">
-        <v>7.521461187214611</v>
+        <v>7.540639269406394</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -1564,7 +1564,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>8.317808219178081</v>
+        <v>8.336986301369864</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1611,7 +1611,7 @@
         <v>0.06</v>
       </c>
       <c r="D8">
-        <v>9.939726027397262</v>
+        <v>9.95890410958904</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -1623,7 +1623,7 @@
         <v>49</v>
       </c>
       <c r="K8">
-        <v>17.934246575342467</v>
+        <v>17.953424657534246</v>
       </c>
       <c r="L8" t="s">
         <v>50</v>
@@ -1673,7 +1673,7 @@
         <v>0.03</v>
       </c>
       <c r="D9">
-        <v>4.372602739726028</v>
+        <v>4.391780821917808</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -1685,7 +1685,7 @@
         <v>52</v>
       </c>
       <c r="K9">
-        <v>8.673972602739726</v>
+        <v>8.693150684931506</v>
       </c>
       <c r="L9" t="s">
         <v>53</v>
@@ -1732,7 +1732,7 @@
         <v>0.15</v>
       </c>
       <c r="D10">
-        <v>4.326027397260274</v>
+        <v>4.345205479452055</v>
       </c>
       <c r="F10" t="s">
         <v>29</v>
@@ -1744,7 +1744,7 @@
         <v>31</v>
       </c>
       <c r="K10">
-        <v>13.301369863013699</v>
+        <v>13.32054794520548</v>
       </c>
       <c r="L10" t="s">
         <v>32</v>
@@ -1788,7 +1788,7 @@
         <v>0.12</v>
       </c>
       <c r="D11">
-        <v>6.755251141552512</v>
+        <v>6.774429223744292</v>
       </c>
       <c r="F11" t="s">
         <v>29</v>
@@ -1800,7 +1800,7 @@
         <v>56</v>
       </c>
       <c r="K11">
-        <v>11.758904109589041</v>
+        <v>11.778082191780822</v>
       </c>
       <c r="L11" t="s">
         <v>35</v>
@@ -1844,7 +1844,7 @@
         <v>0.04</v>
       </c>
       <c r="D12">
-        <v>1.4493150684931506</v>
+        <v>1.4684931506849315</v>
       </c>
       <c r="F12" t="s">
         <v>29</v>
@@ -1856,7 +1856,7 @@
         <v>58</v>
       </c>
       <c r="K12">
-        <v>1.4493150684931506</v>
+        <v>1.4684931506849315</v>
       </c>
       <c r="L12" t="s">
         <v>59</v>
@@ -1906,7 +1906,7 @@
         <v>0.09</v>
       </c>
       <c r="D13">
-        <v>1.4493150684931506</v>
+        <v>1.4684931506849315</v>
       </c>
       <c r="E13">
         <v>6.8</v>
@@ -1921,7 +1921,7 @@
         <v>58</v>
       </c>
       <c r="K13">
-        <v>1.4493150684931506</v>
+        <v>1.4684931506849315</v>
       </c>
       <c r="L13" t="s">
         <v>59</v>
@@ -1974,7 +1974,7 @@
         <v>0.6</v>
       </c>
       <c r="D14">
-        <v>5.260273972602739</v>
+        <v>5.279452054794521</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -1986,7 +1986,7 @@
         <v>63</v>
       </c>
       <c r="K14">
-        <v>6.898630136986301</v>
+        <v>6.917808219178082</v>
       </c>
       <c r="L14" t="s">
         <v>64</v>
@@ -2027,7 +2027,7 @@
         <v>0.1</v>
       </c>
       <c r="D15">
-        <v>2.5328767123287674</v>
+        <v>2.5520547945205476</v>
       </c>
       <c r="E15">
         <v>9.5</v>
@@ -2042,7 +2042,7 @@
         <v>31</v>
       </c>
       <c r="K15">
-        <v>6.1287671232876715</v>
+        <v>6.147945205479452</v>
       </c>
       <c r="L15" t="s">
         <v>32</v>
@@ -2083,7 +2083,7 @@
         <v>0.95</v>
       </c>
       <c r="D16">
-        <v>10.550684931506849</v>
+        <v>10.56986301369863</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -2095,7 +2095,7 @@
         <v>68</v>
       </c>
       <c r="K16">
-        <v>12.841095890410958</v>
+        <v>12.860273972602739</v>
       </c>
       <c r="L16" t="s">
         <v>69</v>
@@ -2142,7 +2142,7 @@
         <v>0.2</v>
       </c>
       <c r="D17">
-        <v>5.898630136986302</v>
+        <v>5.917808219178082</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
@@ -2154,7 +2154,7 @@
         <v>71</v>
       </c>
       <c r="K17">
-        <v>8.775342465753425</v>
+        <v>8.794520547945206</v>
       </c>
       <c r="L17" t="s">
         <v>72</v>
@@ -2198,7 +2198,7 @@
         <v>0.3</v>
       </c>
       <c r="D18">
-        <v>5.606392694063927</v>
+        <v>5.6255707762557075</v>
       </c>
       <c r="F18" t="s">
         <v>29</v>
@@ -2210,7 +2210,7 @@
         <v>63</v>
       </c>
       <c r="K18">
-        <v>7.416438356164384</v>
+        <v>7.435616438356164</v>
       </c>
       <c r="L18" t="s">
         <v>64</v>
@@ -2251,7 +2251,7 @@
         <v>0.95</v>
       </c>
       <c r="D19">
-        <v>10.550684931506849</v>
+        <v>10.56986301369863</v>
       </c>
       <c r="F19" t="s">
         <v>62</v>
@@ -2263,7 +2263,7 @@
         <v>75</v>
       </c>
       <c r="K19">
-        <v>12.841095890410958</v>
+        <v>12.860273972602739</v>
       </c>
       <c r="L19" t="s">
         <v>69</v>
@@ -2313,7 +2313,7 @@
         <v>0.68</v>
       </c>
       <c r="D20">
-        <v>4.932191780821917</v>
+        <v>4.951369863013698</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -2325,7 +2325,7 @@
         <v>77</v>
       </c>
       <c r="K20">
-        <v>6.235616438356164</v>
+        <v>6.254794520547946</v>
       </c>
       <c r="L20" t="s">
         <v>78</v>
@@ -2369,7 +2369,7 @@
         <v>0.87</v>
       </c>
       <c r="D21">
-        <v>14.23835616438356</v>
+        <v>14.257534246575343</v>
       </c>
       <c r="F21" t="s">
         <v>62</v>
@@ -2381,7 +2381,7 @@
         <v>80</v>
       </c>
       <c r="K21">
-        <v>17.632876712328766</v>
+        <v>17.65205479452055</v>
       </c>
       <c r="L21" t="s">
         <v>81</v>
@@ -2428,7 +2428,7 @@
         <v>0.45</v>
       </c>
       <c r="D22">
-        <v>6.742465753424658</v>
+        <v>6.761643835616439</v>
       </c>
       <c r="F22" t="s">
         <v>29</v>
@@ -2440,7 +2440,7 @@
         <v>75</v>
       </c>
       <c r="K22">
-        <v>6.742465753424658</v>
+        <v>6.761643835616439</v>
       </c>
       <c r="L22" t="s">
         <v>69</v>
@@ -2484,7 +2484,7 @@
         <v>0.5</v>
       </c>
       <c r="D23">
-        <v>12.250489236790608</v>
+        <v>12.269667318982387</v>
       </c>
       <c r="F23" t="s">
         <v>62</v>
@@ -2496,7 +2496,7 @@
         <v>84</v>
       </c>
       <c r="K23">
-        <v>13.975342465753425</v>
+        <v>13.994520547945205</v>
       </c>
       <c r="L23" t="s">
         <v>85</v>
@@ -2540,7 +2540,7 @@
         <v>0.04</v>
       </c>
       <c r="D24">
-        <v>7.088584474885844</v>
+        <v>7.107762557077625</v>
       </c>
       <c r="F24" t="s">
         <v>29</v>
@@ -2552,7 +2552,7 @@
         <v>87</v>
       </c>
       <c r="K24">
-        <v>11.758904109589041</v>
+        <v>11.778082191780822</v>
       </c>
       <c r="L24" t="s">
         <v>35</v>
@@ -2602,7 +2602,7 @@
         <v>0.04</v>
       </c>
       <c r="D25">
-        <v>7.363470319634703</v>
+        <v>7.382648401826483</v>
       </c>
       <c r="F25" t="s">
         <v>29</v>
@@ -2614,7 +2614,7 @@
         <v>87</v>
       </c>
       <c r="K25">
-        <v>11.758904109589041</v>
+        <v>11.778082191780822</v>
       </c>
       <c r="L25" t="s">
         <v>35</v>
@@ -2711,7 +2711,7 @@
         <v>0.09</v>
       </c>
       <c r="D27">
-        <v>9.563013698630137</v>
+        <v>9.582191780821917</v>
       </c>
       <c r="F27" t="s">
         <v>29</v>
@@ -2723,7 +2723,7 @@
         <v>75</v>
       </c>
       <c r="K27">
-        <v>10.865753424657534</v>
+        <v>10.884931506849314</v>
       </c>
       <c r="L27" t="s">
         <v>69</v>
@@ -2767,7 +2767,7 @@
         <v>0.09</v>
       </c>
       <c r="D28">
-        <v>9.563013698630137</v>
+        <v>9.582191780821917</v>
       </c>
       <c r="E28">
         <v>8.6</v>
@@ -2782,7 +2782,7 @@
         <v>75</v>
       </c>
       <c r="K28">
-        <v>10.865753424657534</v>
+        <v>10.884931506849314</v>
       </c>
       <c r="L28" t="s">
         <v>69</v>
@@ -2829,7 +2829,7 @@
         <v>0.84</v>
       </c>
       <c r="D29">
-        <v>14.295890410958904</v>
+        <v>14.315068493150685</v>
       </c>
       <c r="F29" t="s">
         <v>62</v>
@@ -2841,7 +2841,7 @@
         <v>80</v>
       </c>
       <c r="K29">
-        <v>17.747945205479454</v>
+        <v>17.767123287671232</v>
       </c>
       <c r="L29" t="s">
         <v>81</v>
@@ -2888,7 +2888,7 @@
         <v>0.03</v>
       </c>
       <c r="D30">
-        <v>7.363470319634704</v>
+        <v>7.382648401826483</v>
       </c>
       <c r="F30" t="s">
         <v>29</v>
@@ -2900,7 +2900,7 @@
         <v>95</v>
       </c>
       <c r="K30">
-        <v>11.758904109589041</v>
+        <v>11.778082191780822</v>
       </c>
       <c r="L30" t="s">
         <v>35</v>
@@ -2944,7 +2944,7 @@
         <v>0.13</v>
       </c>
       <c r="D31">
-        <v>9.419178082191783</v>
+        <v>9.438356164383562</v>
       </c>
       <c r="F31" t="s">
         <v>29</v>
@@ -2956,7 +2956,7 @@
         <v>45</v>
       </c>
       <c r="K31">
-        <v>10.819178082191781</v>
+        <v>10.838356164383562</v>
       </c>
       <c r="L31" t="s">
         <v>46</v>
@@ -3000,7 +3000,7 @@
         <v>0.04</v>
       </c>
       <c r="D32">
-        <v>8.756164383561645</v>
+        <v>8.775342465753425</v>
       </c>
       <c r="F32" t="s">
         <v>29</v>
@@ -3012,7 +3012,7 @@
         <v>99</v>
       </c>
       <c r="K32">
-        <v>12.758904109589041</v>
+        <v>12.778082191780822</v>
       </c>
       <c r="L32" t="s">
         <v>100</v>
@@ -3059,7 +3059,7 @@
         <v>0.15</v>
       </c>
       <c r="D33">
-        <v>14.346118721461186</v>
+        <v>14.365296803652967</v>
       </c>
       <c r="F33" t="s">
         <v>29</v>
@@ -3071,7 +3071,7 @@
         <v>45</v>
       </c>
       <c r="K33">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L33" t="s">
         <v>46</v>
@@ -3121,7 +3121,7 @@
         <v>0.25</v>
       </c>
       <c r="D34">
-        <v>12.374429223744293</v>
+        <v>12.393607305936072</v>
       </c>
       <c r="F34" t="s">
         <v>29</v>
@@ -3133,7 +3133,7 @@
         <v>45</v>
       </c>
       <c r="K34">
-        <v>15.252054794520548</v>
+        <v>15.271232876712329</v>
       </c>
       <c r="L34" t="s">
         <v>46</v>
@@ -3180,7 +3180,7 @@
         <v>0.07</v>
       </c>
       <c r="D35">
-        <v>5.067579908675799</v>
+        <v>5.0867579908675795</v>
       </c>
       <c r="F35" t="s">
         <v>29</v>
@@ -3192,7 +3192,7 @@
         <v>105</v>
       </c>
       <c r="K35">
-        <v>11.506849315068493</v>
+        <v>11.526027397260274</v>
       </c>
       <c r="L35" t="s">
         <v>35</v>
@@ -3239,7 +3239,7 @@
         <v>0.03</v>
       </c>
       <c r="D36">
-        <v>8.417351598173516</v>
+        <v>8.436529680365297</v>
       </c>
       <c r="F36" t="s">
         <v>29</v>
@@ -3251,7 +3251,7 @@
         <v>108</v>
       </c>
       <c r="K36">
-        <v>11.506849315068493</v>
+        <v>11.526027397260274</v>
       </c>
       <c r="L36" t="s">
         <v>35</v>
@@ -3298,7 +3298,7 @@
         <v>0.33</v>
       </c>
       <c r="D37">
-        <v>4.419178082191781</v>
+        <v>4.438356164383562</v>
       </c>
       <c r="F37" t="s">
         <v>29</v>
@@ -3310,7 +3310,7 @@
         <v>31</v>
       </c>
       <c r="K37">
-        <v>13.673972602739726</v>
+        <v>13.693150684931506</v>
       </c>
       <c r="L37" t="s">
         <v>32</v>
@@ -3363,7 +3363,7 @@
         <v>0.75</v>
       </c>
       <c r="D38">
-        <v>13.623287671232877</v>
+        <v>13.642465753424657</v>
       </c>
       <c r="F38" t="s">
         <v>29</v>
@@ -3375,7 +3375,7 @@
         <v>80</v>
       </c>
       <c r="K38">
-        <v>16.4027397260274</v>
+        <v>16.421917808219177</v>
       </c>
       <c r="L38" t="s">
         <v>81</v>
@@ -3422,7 +3422,7 @@
         <v>0.15</v>
       </c>
       <c r="D39">
-        <v>6.755251141552512</v>
+        <v>6.774429223744292</v>
       </c>
       <c r="F39" t="s">
         <v>29</v>
@@ -3434,7 +3434,7 @@
         <v>43</v>
       </c>
       <c r="K39">
-        <v>11.758904109589041</v>
+        <v>11.778082191780822</v>
       </c>
       <c r="L39" t="s">
         <v>35</v>
@@ -3484,7 +3484,7 @@
         <v>0.2</v>
       </c>
       <c r="D40">
-        <v>6.028310502283105</v>
+        <v>6.047488584474887</v>
       </c>
       <c r="E40">
         <v>0.5</v>
@@ -3499,7 +3499,7 @@
         <v>113</v>
       </c>
       <c r="K40">
-        <v>9.756164383561643</v>
+        <v>9.775342465753425</v>
       </c>
       <c r="L40" t="s">
         <v>114</v>
@@ -3543,7 +3543,7 @@
         <v>0.03</v>
       </c>
       <c r="D41">
-        <v>9.021232876712329</v>
+        <v>9.04041095890411</v>
       </c>
       <c r="E41">
         <v>10.1</v>
@@ -3558,7 +3558,7 @@
         <v>116</v>
       </c>
       <c r="K41">
-        <v>15.558904109589042</v>
+        <v>15.578082191780823</v>
       </c>
       <c r="L41" t="s">
         <v>117</v>
@@ -3605,7 +3605,7 @@
         <v>0.39</v>
       </c>
       <c r="D42">
-        <v>7.0511415525114165</v>
+        <v>7.070319634703196</v>
       </c>
       <c r="F42" t="s">
         <v>29</v>
@@ -3617,7 +3617,7 @@
         <v>45</v>
       </c>
       <c r="K42">
-        <v>7.1945205479452055</v>
+        <v>7.213698630136986</v>
       </c>
       <c r="L42" t="s">
         <v>46</v>
@@ -3664,7 +3664,7 @@
         <v>0.4</v>
       </c>
       <c r="D43">
-        <v>7.521461187214612</v>
+        <v>7.540639269406394</v>
       </c>
       <c r="F43" t="s">
         <v>29</v>
@@ -3676,7 +3676,7 @@
         <v>45</v>
       </c>
       <c r="K43">
-        <v>8.317808219178081</v>
+        <v>8.336986301369864</v>
       </c>
       <c r="L43" t="s">
         <v>46</v>
@@ -3720,7 +3720,7 @@
         <v>0.35</v>
       </c>
       <c r="D44">
-        <v>7.521461187214611</v>
+        <v>7.540639269406394</v>
       </c>
       <c r="F44" t="s">
         <v>29</v>
@@ -3732,7 +3732,7 @@
         <v>45</v>
       </c>
       <c r="K44">
-        <v>8.317808219178081</v>
+        <v>8.336986301369864</v>
       </c>
       <c r="L44" t="s">
         <v>46</v>
@@ -3779,7 +3779,7 @@
         <v>0.19</v>
       </c>
       <c r="D45">
-        <v>5.767123287671233</v>
+        <v>5.786301369863014</v>
       </c>
       <c r="F45" t="s">
         <v>29</v>
@@ -3791,7 +3791,7 @@
         <v>122</v>
       </c>
       <c r="K45">
-        <v>5.767123287671233</v>
+        <v>5.786301369863014</v>
       </c>
       <c r="L45" t="s">
         <v>123</v>
@@ -3835,7 +3835,7 @@
         <v>0.95</v>
       </c>
       <c r="D46">
-        <v>10.550684931506849</v>
+        <v>10.56986301369863</v>
       </c>
       <c r="F46" t="s">
         <v>62</v>
@@ -3847,7 +3847,7 @@
         <v>68</v>
       </c>
       <c r="K46">
-        <v>12.841095890410958</v>
+        <v>12.860273972602739</v>
       </c>
       <c r="L46" t="s">
         <v>69</v>
@@ -3894,7 +3894,7 @@
         <v>0.48</v>
       </c>
       <c r="D47">
-        <v>3.16986301369863</v>
+        <v>3.1890410958904107</v>
       </c>
       <c r="F47" t="s">
         <v>62</v>
@@ -3906,7 +3906,7 @@
         <v>126</v>
       </c>
       <c r="K47">
-        <v>3.16986301369863</v>
+        <v>3.1890410958904107</v>
       </c>
       <c r="L47" t="s">
         <v>127</v>
@@ -3950,7 +3950,7 @@
         <v>0.52</v>
       </c>
       <c r="D48">
-        <v>0.336986301369863</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="F48" t="s">
         <v>62</v>
@@ -3962,7 +3962,7 @@
         <v>126</v>
       </c>
       <c r="K48">
-        <v>0.336986301369863</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="L48" t="s">
         <v>127</v>
@@ -4009,7 +4009,7 @@
         <v>0.19</v>
       </c>
       <c r="D49">
-        <v>5.588127853881279</v>
+        <v>5.60730593607306</v>
       </c>
       <c r="F49" t="s">
         <v>29</v>
@@ -4021,7 +4021,7 @@
         <v>130</v>
       </c>
       <c r="K49">
-        <v>6.854794520547945</v>
+        <v>6.873972602739726</v>
       </c>
       <c r="L49" t="s">
         <v>131</v>
@@ -4065,7 +4065,7 @@
         <v>0.47</v>
       </c>
       <c r="D50">
-        <v>11.250489236790608</v>
+        <v>11.269667318982387</v>
       </c>
       <c r="F50" t="s">
         <v>62</v>
@@ -4077,7 +4077,7 @@
         <v>84</v>
       </c>
       <c r="K50">
-        <v>12.575342465753424</v>
+        <v>12.594520547945205</v>
       </c>
       <c r="L50" t="s">
         <v>85</v>
@@ -4121,7 +4121,7 @@
         <v>0.29</v>
       </c>
       <c r="D51">
-        <v>3.9726027397260273</v>
+        <v>3.9917808219178084</v>
       </c>
       <c r="F51" t="s">
         <v>29</v>
@@ -4133,7 +4133,7 @@
         <v>134</v>
       </c>
       <c r="K51">
-        <v>3.9726027397260273</v>
+        <v>3.9917808219178084</v>
       </c>
       <c r="L51" t="s">
         <v>135</v>
@@ -4174,7 +4174,7 @@
         <v>0.13</v>
       </c>
       <c r="D52">
-        <v>9.419178082191781</v>
+        <v>9.438356164383562</v>
       </c>
       <c r="F52" t="s">
         <v>29</v>
@@ -4186,7 +4186,7 @@
         <v>45</v>
       </c>
       <c r="K52">
-        <v>10.819178082191781</v>
+        <v>10.838356164383562</v>
       </c>
       <c r="L52" t="s">
         <v>46</v>
@@ -4230,7 +4230,7 @@
         <v>0.28</v>
       </c>
       <c r="D53">
-        <v>11.786301369863013</v>
+        <v>11.805479452054794</v>
       </c>
       <c r="E53">
         <v>5.9</v>
@@ -4245,7 +4245,7 @@
         <v>138</v>
       </c>
       <c r="K53">
-        <v>11.786301369863013</v>
+        <v>11.805479452054794</v>
       </c>
       <c r="L53" t="s">
         <v>139</v>
@@ -4292,7 +4292,7 @@
         <v>0.4</v>
       </c>
       <c r="D54">
-        <v>5.936986301369863</v>
+        <v>5.956164383561645</v>
       </c>
       <c r="F54" t="s">
         <v>29</v>
@@ -4304,7 +4304,7 @@
         <v>63</v>
       </c>
       <c r="K54">
-        <v>7.912328767123288</v>
+        <v>7.931506849315069</v>
       </c>
       <c r="L54" t="s">
         <v>64</v>
@@ -4348,7 +4348,7 @@
         <v>0.55</v>
       </c>
       <c r="D55">
-        <v>16.700195694716243</v>
+        <v>16.719373776908025</v>
       </c>
       <c r="E55">
         <v>2.9</v>
@@ -4363,7 +4363,7 @@
         <v>142</v>
       </c>
       <c r="K55">
-        <v>20.2986301369863</v>
+        <v>20.317808219178083</v>
       </c>
       <c r="L55" t="s">
         <v>143</v>
@@ -4413,7 +4413,7 @@
         <v>0.15</v>
       </c>
       <c r="D56">
-        <v>5.802739726027397</v>
+        <v>5.821917808219179</v>
       </c>
       <c r="F56" t="s">
         <v>29</v>
@@ -4425,7 +4425,7 @@
         <v>145</v>
       </c>
       <c r="K56">
-        <v>5.802739726027397</v>
+        <v>5.821917808219178</v>
       </c>
       <c r="L56" t="s">
         <v>146</v>
@@ -4466,7 +4466,7 @@
         <v>0.58</v>
       </c>
       <c r="D57">
-        <v>5.208219178082191</v>
+        <v>5.227397260273973</v>
       </c>
       <c r="F57" t="s">
         <v>62</v>
@@ -4478,7 +4478,7 @@
         <v>75</v>
       </c>
       <c r="K57">
-        <v>5.208219178082191</v>
+        <v>5.227397260273973</v>
       </c>
       <c r="L57" t="s">
         <v>69</v>
@@ -4519,7 +4519,7 @@
         <v>0.18</v>
       </c>
       <c r="D58">
-        <v>0.6082191780821918</v>
+        <v>0.6273972602739726</v>
       </c>
       <c r="F58" t="s">
         <v>29</v>
@@ -4531,7 +4531,7 @@
         <v>145</v>
       </c>
       <c r="K58">
-        <v>0.6082191780821918</v>
+        <v>0.6273972602739726</v>
       </c>
       <c r="L58" t="s">
         <v>146</v>
@@ -4581,7 +4581,7 @@
         <v>0.55</v>
       </c>
       <c r="D59">
-        <v>14.346118721461186</v>
+        <v>14.365296803652967</v>
       </c>
       <c r="F59" t="s">
         <v>62</v>
@@ -4593,7 +4593,7 @@
         <v>45</v>
       </c>
       <c r="K59">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L59" t="s">
         <v>46</v>
@@ -4640,7 +4640,7 @@
         <v>0.55</v>
       </c>
       <c r="D60">
-        <v>14.346118721461186</v>
+        <v>14.365296803652967</v>
       </c>
       <c r="F60" t="s">
         <v>62</v>
@@ -4652,7 +4652,7 @@
         <v>45</v>
       </c>
       <c r="K60">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L60" t="s">
         <v>46</v>
@@ -4699,7 +4699,7 @@
         <v>0.6</v>
       </c>
       <c r="D61">
-        <v>14.346118721461186</v>
+        <v>14.365296803652967</v>
       </c>
       <c r="F61" t="s">
         <v>62</v>
@@ -4711,7 +4711,7 @@
         <v>45</v>
       </c>
       <c r="K61">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L61" t="s">
         <v>46</v>
@@ -4758,7 +4758,7 @@
         <v>0.29</v>
       </c>
       <c r="D62">
-        <v>13.092237442922375</v>
+        <v>13.111415525114154</v>
       </c>
       <c r="F62" t="s">
         <v>29</v>
@@ -4770,7 +4770,7 @@
         <v>45</v>
       </c>
       <c r="K62">
-        <v>16.328767123287673</v>
+        <v>16.34794520547945</v>
       </c>
       <c r="L62" t="s">
         <v>46</v>
@@ -4817,7 +4817,7 @@
         <v>0.34</v>
       </c>
       <c r="D63">
-        <v>14.346118721461186</v>
+        <v>14.365296803652967</v>
       </c>
       <c r="F63" t="s">
         <v>29</v>
@@ -4829,7 +4829,7 @@
         <v>45</v>
       </c>
       <c r="K63">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L63" t="s">
         <v>46</v>
@@ -4876,7 +4876,7 @@
         <v>0.49</v>
       </c>
       <c r="D64">
-        <v>6.087671232876712</v>
+        <v>6.106849315068493</v>
       </c>
       <c r="F64" t="s">
         <v>29</v>
@@ -4888,7 +4888,7 @@
         <v>155</v>
       </c>
       <c r="K64">
-        <v>8.03013698630137</v>
+        <v>8.04931506849315</v>
       </c>
       <c r="L64" t="s">
         <v>156</v>
@@ -4929,7 +4929,7 @@
         <v>0.62</v>
       </c>
       <c r="D65">
-        <v>14.346118721461186</v>
+        <v>14.365296803652967</v>
       </c>
       <c r="F65" t="s">
         <v>62</v>
@@ -4941,7 +4941,7 @@
         <v>45</v>
       </c>
       <c r="K65">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L65" t="s">
         <v>46</v>
@@ -4988,7 +4988,7 @@
         <v>0.7</v>
       </c>
       <c r="D66">
-        <v>13.31311154598826</v>
+        <v>13.332289628180039</v>
       </c>
       <c r="F66" t="s">
         <v>62</v>
@@ -5000,7 +5000,7 @@
         <v>84</v>
       </c>
       <c r="K66">
-        <v>15.463013698630137</v>
+        <v>15.482191780821918</v>
       </c>
       <c r="L66" t="s">
         <v>85</v>
@@ -5050,7 +5050,7 @@
         <v>0.49</v>
       </c>
       <c r="D67">
-        <v>2.506849315068493</v>
+        <v>2.526027397260274</v>
       </c>
       <c r="E67">
         <v>1.5</v>
@@ -5065,7 +5065,7 @@
         <v>160</v>
       </c>
       <c r="K67">
-        <v>2.506849315068493</v>
+        <v>2.526027397260274</v>
       </c>
       <c r="L67" t="s">
         <v>161</v>
@@ -5106,7 +5106,7 @@
         <v>0.15</v>
       </c>
       <c r="D68">
-        <v>4.326027397260274</v>
+        <v>4.345205479452055</v>
       </c>
       <c r="F68" t="s">
         <v>29</v>
@@ -5118,7 +5118,7 @@
         <v>31</v>
       </c>
       <c r="K68">
-        <v>13.301369863013699</v>
+        <v>13.32054794520548</v>
       </c>
       <c r="L68" t="s">
         <v>32</v>
@@ -5162,7 +5162,7 @@
         <v>0.05</v>
       </c>
       <c r="D69">
-        <v>1.4493150684931506</v>
+        <v>1.4684931506849315</v>
       </c>
       <c r="E69">
         <v>6.8</v>
@@ -5177,7 +5177,7 @@
         <v>164</v>
       </c>
       <c r="K69">
-        <v>1.4493150684931506</v>
+        <v>1.4684931506849315</v>
       </c>
       <c r="L69" t="s">
         <v>165</v>
@@ -5224,7 +5224,7 @@
         <v>0.29</v>
       </c>
       <c r="D70">
-        <v>3.9726027397260273</v>
+        <v>3.9917808219178084</v>
       </c>
       <c r="F70" t="s">
         <v>29</v>
@@ -5236,7 +5236,7 @@
         <v>134</v>
       </c>
       <c r="K70">
-        <v>3.9726027397260273</v>
+        <v>3.9917808219178084</v>
       </c>
       <c r="L70" t="s">
         <v>135</v>
@@ -5280,7 +5280,7 @@
         <v>0.7</v>
       </c>
       <c r="D71">
-        <v>3.880547945205479</v>
+        <v>3.89972602739726</v>
       </c>
       <c r="F71" t="s">
         <v>62</v>
@@ -5292,7 +5292,7 @@
         <v>168</v>
       </c>
       <c r="K71">
-        <v>8.027397260273972</v>
+        <v>8.046575342465754</v>
       </c>
       <c r="L71" t="s">
         <v>64</v>
@@ -5333,7 +5333,7 @@
         <v>0.2</v>
       </c>
       <c r="D72">
-        <v>5.442922374429224</v>
+        <v>5.4621004566210045</v>
       </c>
       <c r="F72" t="s">
         <v>29</v>
@@ -5345,7 +5345,7 @@
         <v>170</v>
       </c>
       <c r="K72">
-        <v>7.789041095890411</v>
+        <v>7.808219178082192</v>
       </c>
       <c r="L72" t="s">
         <v>171</v>
@@ -5386,7 +5386,7 @@
         <v>0.4</v>
       </c>
       <c r="D73">
-        <v>10.781506849315068</v>
+        <v>10.800684931506847</v>
       </c>
       <c r="F73" t="s">
         <v>29</v>
@@ -5398,7 +5398,7 @@
         <v>173</v>
       </c>
       <c r="K73">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L73" t="s">
         <v>46</v>
@@ -5448,7 +5448,7 @@
         <v>0.12</v>
       </c>
       <c r="D74">
-        <v>7.073059360730594</v>
+        <v>7.092237442922374</v>
       </c>
       <c r="F74" t="s">
         <v>29</v>
@@ -5460,7 +5460,7 @@
         <v>175</v>
       </c>
       <c r="K74">
-        <v>8.734246575342466</v>
+        <v>8.753424657534246</v>
       </c>
       <c r="L74" t="s">
         <v>176</v>
@@ -5478,16 +5478,16 @@
         <v>-4.32834</v>
       </c>
       <c r="U74">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="V74">
-        <v>0.86</v>
+        <v>0.69</v>
       </c>
       <c r="W74">
+        <v>0.78</v>
+      </c>
+      <c r="X74">
         <v>0.89</v>
-      </c>
-      <c r="X74">
-        <v>0.96</v>
       </c>
       <c r="AB74">
         <v>0.3</v>
@@ -5501,7 +5501,7 @@
         <v>0.12</v>
       </c>
       <c r="D75">
-        <v>7.073059360730594</v>
+        <v>7.092237442922374</v>
       </c>
       <c r="F75" t="s">
         <v>29</v>
@@ -5513,7 +5513,7 @@
         <v>175</v>
       </c>
       <c r="K75">
-        <v>8.734246575342466</v>
+        <v>8.753424657534246</v>
       </c>
       <c r="L75" t="s">
         <v>176</v>
@@ -5531,16 +5531,16 @@
         <v>6.79993</v>
       </c>
       <c r="U75">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="V75">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="W75">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="X75">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="AB75">
         <v>0.15</v>
@@ -5554,7 +5554,7 @@
         <v>0.37</v>
       </c>
       <c r="D76">
-        <v>4.502739726027397</v>
+        <v>4.521917808219178</v>
       </c>
       <c r="F76" t="s">
         <v>29</v>
@@ -5566,7 +5566,7 @@
         <v>31</v>
       </c>
       <c r="K76">
-        <v>14.008219178082191</v>
+        <v>14.027397260273972</v>
       </c>
       <c r="L76" t="s">
         <v>32</v>
@@ -5616,7 +5616,7 @@
         <v>0.19</v>
       </c>
       <c r="D77">
-        <v>7.466666666666666</v>
+        <v>7.485844748858447</v>
       </c>
       <c r="F77" t="s">
         <v>29</v>
@@ -5628,7 +5628,7 @@
         <v>45</v>
       </c>
       <c r="K77">
-        <v>7.890410958904109</v>
+        <v>7.909589041095891</v>
       </c>
       <c r="L77" t="s">
         <v>46</v>
@@ -5669,7 +5669,7 @@
         <v>0.3</v>
       </c>
       <c r="D78">
-        <v>3.88972602739726</v>
+        <v>3.9089041095890407</v>
       </c>
       <c r="F78" t="s">
         <v>29</v>
@@ -5681,7 +5681,7 @@
         <v>31</v>
       </c>
       <c r="K78">
-        <v>11.556164383561644</v>
+        <v>11.575342465753424</v>
       </c>
       <c r="L78" t="s">
         <v>32</v>
@@ -5728,7 +5728,7 @@
         <v>0.75</v>
       </c>
       <c r="D79">
-        <v>5.189041095890411</v>
+        <v>5.208219178082191</v>
       </c>
       <c r="E79">
         <v>2.9</v>
@@ -5743,7 +5743,7 @@
         <v>182</v>
       </c>
       <c r="K79">
-        <v>5.189041095890411</v>
+        <v>5.208219178082191</v>
       </c>
       <c r="L79" t="s">
         <v>183</v>
@@ -5784,7 +5784,7 @@
         <v>0.56</v>
       </c>
       <c r="D80">
-        <v>10.781506849315068</v>
+        <v>10.800684931506849</v>
       </c>
       <c r="F80" t="s">
         <v>62</v>
@@ -5796,7 +5796,7 @@
         <v>173</v>
       </c>
       <c r="K80">
-        <v>19.18082191780822</v>
+        <v>19.2</v>
       </c>
       <c r="L80" t="s">
         <v>46</v>
@@ -5846,7 +5846,7 @@
         <v>0.37</v>
       </c>
       <c r="D81">
-        <v>4.419178082191781</v>
+        <v>4.438356164383562</v>
       </c>
       <c r="F81" t="s">
         <v>29</v>
@@ -5858,7 +5858,7 @@
         <v>31</v>
       </c>
       <c r="K81">
-        <v>13.673972602739726</v>
+        <v>13.693150684931506</v>
       </c>
       <c r="L81" t="s">
         <v>32</v>
@@ -5908,7 +5908,7 @@
         <v>0.04</v>
       </c>
       <c r="D82">
-        <v>3.3431506849315067</v>
+        <v>3.3623287671232878</v>
       </c>
       <c r="F82" t="s">
         <v>29</v>
@@ -5920,7 +5920,7 @@
         <v>31</v>
       </c>
       <c r="K82">
-        <v>9.36986301369863</v>
+        <v>9.389041095890411</v>
       </c>
       <c r="L82" t="s">
         <v>32</v>
@@ -5964,7 +5964,7 @@
         <v>0.5</v>
       </c>
       <c r="D83">
-        <v>7.052054794520548</v>
+        <v>7.071232876712329</v>
       </c>
       <c r="F83" t="s">
         <v>62</v>
@@ -5976,7 +5976,7 @@
         <v>188</v>
       </c>
       <c r="K83">
-        <v>7.052054794520548</v>
+        <v>7.071232876712329</v>
       </c>
       <c r="L83" t="s">
         <v>188</v>
@@ -6014,7 +6014,7 @@
         <v>0.56</v>
       </c>
       <c r="D84">
-        <v>7.924657534246576</v>
+        <v>7.943835616438356</v>
       </c>
       <c r="E84">
         <v>4.9</v>
@@ -6029,7 +6029,7 @@
         <v>191</v>
       </c>
       <c r="K84">
-        <v>8.424657534246576</v>
+        <v>8.443835616438356</v>
       </c>
       <c r="L84" t="s">
         <v>192</v>
@@ -6076,7 +6076,7 @@
         <v>0.7</v>
       </c>
       <c r="D85">
-        <v>13.206262230919764</v>
+        <v>13.225440313111546</v>
       </c>
       <c r="F85" t="s">
         <v>29</v>
@@ -6088,7 +6088,7 @@
         <v>84</v>
       </c>
       <c r="K85">
-        <v>15.295890410958904</v>
+        <v>15.315068493150685</v>
       </c>
       <c r="L85" t="s">
         <v>85</v>
@@ -6138,7 +6138,7 @@
         <v>0.6</v>
       </c>
       <c r="D86">
-        <v>16.02818003913894</v>
+        <v>16.047358121330724</v>
       </c>
       <c r="F86" t="s">
         <v>62</v>
@@ -6150,7 +6150,7 @@
         <v>84</v>
       </c>
       <c r="K86">
-        <v>19.246575342465754</v>
+        <v>19.265753424657536</v>
       </c>
       <c r="L86" t="s">
         <v>85</v>
@@ -6200,7 +6200,7 @@
         <v>0.6</v>
       </c>
       <c r="D87">
-        <v>9.256751467710373</v>
+        <v>9.275929549902154</v>
       </c>
       <c r="F87" t="s">
         <v>62</v>
@@ -6212,7 +6212,7 @@
         <v>84</v>
       </c>
       <c r="K87">
-        <v>9.868493150684932</v>
+        <v>9.887671232876713</v>
       </c>
       <c r="L87" t="s">
         <v>85</v>
@@ -6253,7 +6253,7 @@
         <v>0.25</v>
       </c>
       <c r="D88">
-        <v>7.184931506849315</v>
+        <v>7.204109589041096</v>
       </c>
       <c r="F88" t="s">
         <v>29</v>
@@ -6265,7 +6265,7 @@
         <v>116</v>
       </c>
       <c r="K88">
-        <v>9.271232876712329</v>
+        <v>9.29041095890411</v>
       </c>
       <c r="L88" t="s">
         <v>117</v>
@@ -6309,7 +6309,7 @@
         <v>0.25</v>
       </c>
       <c r="D89">
-        <v>7.184931506849315</v>
+        <v>7.204109589041096</v>
       </c>
       <c r="F89" t="s">
         <v>29</v>
@@ -6321,7 +6321,7 @@
         <v>116</v>
       </c>
       <c r="K89">
-        <v>9.271232876712329</v>
+        <v>9.29041095890411</v>
       </c>
       <c r="L89" t="s">
         <v>117</v>
@@ -6365,7 +6365,7 @@
         <v>0.45</v>
       </c>
       <c r="D90">
-        <v>6</v>
+        <v>6.0191780821917815</v>
       </c>
       <c r="E90">
         <v>0.5</v>
@@ -6380,7 +6380,7 @@
         <v>199</v>
       </c>
       <c r="K90">
-        <v>8.624657534246575</v>
+        <v>8.643835616438356</v>
       </c>
       <c r="L90" t="s">
         <v>200</v>
@@ -6424,7 +6424,7 @@
         <v>0.57</v>
       </c>
       <c r="D91">
-        <v>16.02818003913894</v>
+        <v>16.047358121330724</v>
       </c>
       <c r="F91" t="s">
         <v>62</v>
@@ -6436,7 +6436,7 @@
         <v>84</v>
       </c>
       <c r="K91">
-        <v>19.246575342465754</v>
+        <v>19.265753424657536</v>
       </c>
       <c r="L91" t="s">
         <v>85</v>
@@ -6483,7 +6483,7 @@
         <v>0.18</v>
       </c>
       <c r="D92">
-        <v>7.175342465753424</v>
+        <v>7.1945205479452055</v>
       </c>
       <c r="F92" t="s">
         <v>29</v>
@@ -6495,7 +6495,7 @@
         <v>203</v>
       </c>
       <c r="K92">
-        <v>11.843835616438357</v>
+        <v>11.863013698630137</v>
       </c>
       <c r="L92" t="s">
         <v>204</v>
@@ -6542,7 +6542,7 @@
         <v>0.15</v>
       </c>
       <c r="D93">
-        <v>8.677260273972603</v>
+        <v>8.696438356164384</v>
       </c>
       <c r="F93" t="s">
         <v>29</v>
@@ -6554,7 +6554,7 @@
         <v>206</v>
       </c>
       <c r="K93">
-        <v>9.89041095890411</v>
+        <v>9.90958904109589</v>
       </c>
       <c r="L93" t="s">
         <v>207</v>
@@ -6595,7 +6595,7 @@
         <v>0.5</v>
       </c>
       <c r="D94">
-        <v>3.9383561643835616</v>
+        <v>3.9575342465753423</v>
       </c>
       <c r="F94" t="s">
         <v>62</v>
@@ -6607,7 +6607,7 @@
         <v>209</v>
       </c>
       <c r="K94">
-        <v>6.295890410958904</v>
+        <v>6.315068493150685</v>
       </c>
       <c r="L94" t="s">
         <v>210</v>
@@ -6651,7 +6651,7 @@
         <v>0.88</v>
       </c>
       <c r="D95">
-        <v>14.294520547945204</v>
+        <v>14.313698630136987</v>
       </c>
       <c r="E95">
         <v>7</v>
@@ -6666,7 +6666,7 @@
         <v>80</v>
       </c>
       <c r="K95">
-        <v>17.745205479452054</v>
+        <v>17.764383561643836</v>
       </c>
       <c r="L95" t="s">
         <v>81</v>
@@ -6716,7 +6716,7 @@
         <v>0.63</v>
       </c>
       <c r="D96">
-        <v>16.02818003913894</v>
+        <v>16.047358121330724</v>
       </c>
       <c r="F96" t="s">
         <v>62</v>
@@ -6728,7 +6728,7 @@
         <v>84</v>
       </c>
       <c r="K96">
-        <v>19.246575342465754</v>
+        <v>19.265753424657536</v>
       </c>
       <c r="L96" t="s">
         <v>85</v>
@@ -6775,7 +6775,7 @@
         <v>0.5</v>
       </c>
       <c r="D97">
-        <v>1.7780821917808218</v>
+        <v>1.7972602739726027</v>
       </c>
       <c r="E97">
         <v>1.8</v>
@@ -6790,7 +6790,7 @@
         <v>214</v>
       </c>
       <c r="K97">
-        <v>1.7780821917808218</v>
+        <v>1.7972602739726027</v>
       </c>
       <c r="L97" t="s">
         <v>214</v>
@@ -6822,7 +6822,7 @@
         <v>0.35</v>
       </c>
       <c r="D98">
-        <v>8.643835616438356</v>
+        <v>8.663013698630138</v>
       </c>
       <c r="F98" t="s">
         <v>29</v>
@@ -6834,7 +6834,7 @@
         <v>75</v>
       </c>
       <c r="K98">
-        <v>9.027397260273972</v>
+        <v>9.046575342465754</v>
       </c>
       <c r="L98" t="s">
         <v>69</v>
@@ -6875,7 +6875,7 @@
         <v>0.48</v>
       </c>
       <c r="D99">
-        <v>5.225753424657534</v>
+        <v>5.244931506849316</v>
       </c>
       <c r="F99" t="s">
         <v>62</v>
@@ -6887,7 +6887,7 @@
         <v>218</v>
       </c>
       <c r="K99">
-        <v>5.767123287671233</v>
+        <v>5.786301369863014</v>
       </c>
       <c r="L99" t="s">
         <v>219</v>
@@ -6937,7 +6937,7 @@
         <v>0.6</v>
       </c>
       <c r="D100">
-        <v>7.565166340508807</v>
+        <v>7.584344422700587</v>
       </c>
       <c r="F100" t="s">
         <v>29</v>
@@ -6949,7 +6949,7 @@
         <v>84</v>
       </c>
       <c r="K100">
-        <v>7.909589041095891</v>
+        <v>7.928767123287671</v>
       </c>
       <c r="L100" t="s">
         <v>85</v>
@@ -6990,7 +6990,7 @@
         <v>0.28</v>
       </c>
       <c r="D101">
-        <v>5.225753424657534</v>
+        <v>5.244931506849316</v>
       </c>
       <c r="F101" t="s">
         <v>29</v>
@@ -7002,7 +7002,7 @@
         <v>218</v>
       </c>
       <c r="K101">
-        <v>5.767123287671233</v>
+        <v>5.786301369863014</v>
       </c>
       <c r="L101" t="s">
         <v>219</v>
@@ -7049,7 +7049,7 @@
         <v>0.96</v>
       </c>
       <c r="D102">
-        <v>9.252054794520548</v>
+        <v>9.271232876712329</v>
       </c>
       <c r="F102" t="s">
         <v>62</v>
@@ -7061,7 +7061,7 @@
         <v>223</v>
       </c>
       <c r="K102">
-        <v>9.252054794520548</v>
+        <v>9.271232876712329</v>
       </c>
       <c r="L102" t="s">
         <v>224</v>
@@ -7102,7 +7102,7 @@
         <v>0.95</v>
       </c>
       <c r="D103">
-        <v>10.550684931506849</v>
+        <v>10.56986301369863</v>
       </c>
       <c r="F103" t="s">
         <v>62</v>
@@ -7114,7 +7114,7 @@
         <v>75</v>
       </c>
       <c r="K103">
-        <v>12.841095890410958</v>
+        <v>12.860273972602739</v>
       </c>
       <c r="L103" t="s">
         <v>69</v>
@@ -7164,7 +7164,7 @@
         <v>0.45</v>
       </c>
       <c r="D104">
-        <v>5.984246575342466</v>
+        <v>6.0034246575342465</v>
       </c>
       <c r="F104" t="s">
         <v>29</v>
@@ -7176,7 +7176,7 @@
         <v>227</v>
       </c>
       <c r="K104">
-        <v>9.652054794520549</v>
+        <v>9.67123287671233</v>
       </c>
       <c r="L104" t="s">
         <v>228</v>
@@ -7223,7 +7223,7 @@
         <v>0.65</v>
       </c>
       <c r="D105">
-        <v>7.521461187214611</v>
+        <v>7.540639269406394</v>
       </c>
       <c r="F105" t="s">
         <v>62</v>
@@ -7235,7 +7235,7 @@
         <v>45</v>
       </c>
       <c r="K105">
-        <v>8.317808219178081</v>
+        <v>8.336986301369864</v>
       </c>
       <c r="L105" t="s">
         <v>46</v>
@@ -7282,7 +7282,7 @@
         <v>0.33</v>
       </c>
       <c r="D106">
-        <v>3.0969863013698626</v>
+        <v>3.1161643835616433</v>
       </c>
       <c r="E106">
         <v>11.3</v>
@@ -7297,7 +7297,7 @@
         <v>231</v>
       </c>
       <c r="K106">
-        <v>4.441095890410959</v>
+        <v>4.46027397260274</v>
       </c>
       <c r="L106" t="s">
         <v>232</v>
@@ -7338,7 +7338,7 @@
         <v>0.85</v>
       </c>
       <c r="D107">
-        <v>5.720547945205479</v>
+        <v>5.739726027397261</v>
       </c>
       <c r="F107" t="s">
         <v>62</v>
@@ -7350,7 +7350,7 @@
         <v>235</v>
       </c>
       <c r="K107">
-        <v>5.720547945205479</v>
+        <v>5.739726027397261</v>
       </c>
       <c r="L107" t="s">
         <v>235</v>
@@ -7391,7 +7391,7 @@
         <v>0.68</v>
       </c>
       <c r="D108">
-        <v>7.924657534246576</v>
+        <v>7.943835616438356</v>
       </c>
       <c r="F108" t="s">
         <v>62</v>
@@ -7403,7 +7403,7 @@
         <v>191</v>
       </c>
       <c r="K108">
-        <v>8.424657534246576</v>
+        <v>8.443835616438356</v>
       </c>
       <c r="L108" t="s">
         <v>192</v>
@@ -7444,7 +7444,7 @@
         <v>0.34</v>
       </c>
       <c r="D109">
-        <v>8.96986301369863</v>
+        <v>8.98904109589041</v>
       </c>
       <c r="F109" t="s">
         <v>29</v>
@@ -7456,7 +7456,7 @@
         <v>238</v>
       </c>
       <c r="K109">
-        <v>8.96986301369863</v>
+        <v>8.98904109589041</v>
       </c>
       <c r="L109" t="s">
         <v>239</v>
@@ -7500,7 +7500,7 @@
         <v>0.47</v>
       </c>
       <c r="D110">
-        <v>3.026712328767123</v>
+        <v>3.045890410958904</v>
       </c>
       <c r="E110">
         <v>9.5</v>
@@ -7515,7 +7515,7 @@
         <v>31</v>
       </c>
       <c r="K110">
-        <v>8.104109589041096</v>
+        <v>8.123287671232877</v>
       </c>
       <c r="L110" t="s">
         <v>32</v>
@@ -7559,7 +7559,7 @@
         <v>0.59</v>
       </c>
       <c r="D111">
-        <v>2.34337899543379</v>
+        <v>2.3625570776255707</v>
       </c>
       <c r="F111" t="s">
         <v>62</v>
@@ -7571,7 +7571,7 @@
         <v>63</v>
       </c>
       <c r="K111">
-        <v>2.515068493150685</v>
+        <v>2.5342465753424657</v>
       </c>
       <c r="L111" t="s">
         <v>64</v>
@@ -7618,7 +7618,7 @@
         <v>0.69</v>
       </c>
       <c r="D112">
-        <v>11.12720156555773</v>
+        <v>11.14637964774951</v>
       </c>
       <c r="F112" t="s">
         <v>62</v>
@@ -7630,7 +7630,7 @@
         <v>84</v>
       </c>
       <c r="K112">
-        <v>12.402739726027397</v>
+        <v>12.421917808219177</v>
       </c>
       <c r="L112" t="s">
         <v>85</v>
@@ -7674,7 +7674,7 @@
         <v>0.03</v>
       </c>
       <c r="D113">
-        <v>5.698630136986302</v>
+        <v>5.717808219178083</v>
       </c>
       <c r="E113">
         <v>9.5</v>
@@ -7689,7 +7689,7 @@
         <v>245</v>
       </c>
       <c r="K113">
-        <v>15.095890410958905</v>
+        <v>15.115068493150686</v>
       </c>
       <c r="L113" t="s">
         <v>246</v>
